--- a/gcmc_data_codes/Sensitivity analysis/figure8.xlsx
+++ b/gcmc_data_codes/Sensitivity analysis/figure8.xlsx
@@ -425,37 +425,37 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.09279336734693877</v>
+        <v>0.07644628099173553</v>
       </c>
       <c r="C2">
-        <v>0.09275793650793651</v>
+        <v>0.0764139979338843</v>
       </c>
       <c r="D2">
-        <v>0.09250992063492064</v>
+        <v>0.07634943181818182</v>
       </c>
       <c r="E2">
-        <v>0.09222647392290249</v>
+        <v>0.0762525826446281</v>
       </c>
       <c r="F2">
-        <v>0.09268707482993198</v>
+        <v>0.07628486570247933</v>
       </c>
       <c r="G2">
-        <v>0.09311224489795919</v>
+        <v>0.07644628099173553</v>
       </c>
       <c r="H2">
-        <v>0.09367913832199547</v>
+        <v>0.07654313016528926</v>
       </c>
       <c r="I2">
-        <v>0.09392715419501134</v>
+        <v>0.07696280991735537</v>
       </c>
       <c r="J2">
-        <v>0.0946357709750567</v>
+        <v>0.07741477272727272</v>
       </c>
       <c r="K2">
-        <v>0.0954861111111111</v>
+        <v>0.07789901859504132</v>
       </c>
       <c r="L2">
-        <v>0.09654903628117914</v>
+        <v>0.0786092458677686</v>
       </c>
     </row>
     <row r="3">
@@ -465,37 +465,37 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.3006306689342403</v>
+        <v>0.2730178202479339</v>
       </c>
       <c r="C3">
-        <v>0.2952097505668934</v>
+        <v>0.2686596074380165</v>
       </c>
       <c r="D3">
-        <v>0.2848639455782313</v>
+        <v>0.2574573863636364</v>
       </c>
       <c r="E3">
-        <v>0.2689200680272109</v>
+        <v>0.2437370867768595</v>
       </c>
       <c r="F3">
-        <v>0.2523030045351474</v>
+        <v>0.2239798553719008</v>
       </c>
       <c r="G3">
-        <v>0.2329577664399093</v>
+        <v>0.2051911157024793</v>
       </c>
       <c r="H3">
-        <v>0.2120535714285714</v>
+        <v>0.1870157541322314</v>
       </c>
       <c r="I3">
-        <v>0.1915745464852608</v>
+        <v>0.1673876549586777</v>
       </c>
       <c r="J3">
-        <v>0.1725481859410431</v>
+        <v>0.1500839359504132</v>
       </c>
       <c r="K3">
-        <v>0.1564271541950113</v>
+        <v>0.1358793904958678</v>
       </c>
       <c r="L3">
-        <v>0.1437074829931973</v>
+        <v>0.1228693181818182</v>
       </c>
     </row>
   </sheetData>
@@ -577,37 +577,37 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.09279336734693877</v>
+        <v>0.07644628099173553</v>
       </c>
       <c r="C2">
-        <v>0.09279336734693877</v>
+        <v>0.07638171487603305</v>
       </c>
       <c r="D2">
-        <v>0.09325396825396826</v>
+        <v>0.07512267561983471</v>
       </c>
       <c r="E2">
-        <v>0.09350198412698413</v>
+        <v>0.07366993801652892</v>
       </c>
       <c r="F2">
-        <v>0.09204931972789115</v>
+        <v>0.07231404958677685</v>
       </c>
       <c r="G2">
-        <v>0.09346655328798185</v>
+        <v>0.07040934917355372</v>
       </c>
       <c r="H2">
-        <v>0.0939625850340136</v>
+        <v>0.07115185950413223</v>
       </c>
       <c r="I2">
-        <v>0.09481292517006802</v>
+        <v>0.0699896694214876</v>
       </c>
       <c r="J2">
-        <v>0.09328939909297052</v>
+        <v>0.06895661157024793</v>
       </c>
       <c r="K2">
-        <v>0.0586734693877551</v>
+        <v>0.049974173553719</v>
       </c>
       <c r="L2">
-        <v>0.0954861111111111</v>
+        <v>0.07086131198347108</v>
       </c>
     </row>
     <row r="3">
@@ -617,37 +617,37 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.3006306689342403</v>
+        <v>0.2730178202479339</v>
       </c>
       <c r="C3">
-        <v>0.3013038548752834</v>
+        <v>0.2738571797520661</v>
       </c>
       <c r="D3">
-        <v>0.3022250566893424</v>
+        <v>0.2748902376033058</v>
       </c>
       <c r="E3">
-        <v>0.3035359977324263</v>
+        <v>0.275987861570248</v>
       </c>
       <c r="F3">
-        <v>0.3050240929705215</v>
+        <v>0.2771823347107438</v>
       </c>
       <c r="G3">
-        <v>0.3062996031746032</v>
+        <v>0.2788610537190083</v>
       </c>
       <c r="H3">
-        <v>0.3072562358276644</v>
+        <v>0.2801523760330579</v>
       </c>
       <c r="I3">
-        <v>0.308531746031746</v>
+        <v>0.2814114152892562</v>
       </c>
       <c r="J3">
-        <v>0.3104804421768708</v>
+        <v>0.2832192665289256</v>
       </c>
       <c r="K3">
-        <v>0.3138463718820862</v>
+        <v>0.2863184400826446</v>
       </c>
       <c r="L3">
-        <v>0.3160076530612245</v>
+        <v>0.2884491219008264</v>
       </c>
     </row>
   </sheetData>
@@ -729,37 +729,37 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.09279336734693877</v>
+        <v>0.07644628099173553</v>
       </c>
       <c r="C2">
-        <v>0.09282879818594104</v>
+        <v>0.07634943181818182</v>
       </c>
       <c r="D2">
-        <v>0.09346655328798185</v>
+        <v>0.07515495867768596</v>
       </c>
       <c r="E2">
-        <v>0.09431689342403628</v>
+        <v>0.07425103305785125</v>
       </c>
       <c r="F2">
-        <v>0.09406887755102041</v>
+        <v>0.07337939049586777</v>
       </c>
       <c r="G2">
-        <v>0.09686791383219955</v>
+        <v>0.07263688016528926</v>
       </c>
       <c r="H2">
-        <v>0.0988874716553288</v>
+        <v>0.0740573347107438</v>
       </c>
       <c r="I2">
-        <v>0.101296768707483</v>
+        <v>0.07444473140495868</v>
       </c>
       <c r="J2">
-        <v>0.1014384920634921</v>
+        <v>0.07428331611570248</v>
       </c>
       <c r="K2">
-        <v>0.06242913832199547</v>
+        <v>0.05291193181818182</v>
       </c>
       <c r="L2">
-        <v>0.1047689909297052</v>
+        <v>0.07651084710743801</v>
       </c>
     </row>
     <row r="3">
@@ -769,37 +769,37 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.3006306689342403</v>
+        <v>0.2730178202479339</v>
       </c>
       <c r="C3">
-        <v>0.2963081065759637</v>
+        <v>0.2699509297520661</v>
       </c>
       <c r="D3">
-        <v>0.2868835034013605</v>
+        <v>0.2596526342975207</v>
       </c>
       <c r="E3">
-        <v>0.2726757369614513</v>
+        <v>0.2476756198347107</v>
       </c>
       <c r="F3">
-        <v>0.2577593537414966</v>
+        <v>0.2291451446280992</v>
       </c>
       <c r="G3">
-        <v>0.2394770408163265</v>
+        <v>0.2111957644628099</v>
       </c>
       <c r="H3">
-        <v>0.2197066326530612</v>
+        <v>0.1947959710743802</v>
       </c>
       <c r="I3">
-        <v>0.1997945011337869</v>
+        <v>0.1757489669421488</v>
       </c>
       <c r="J3">
-        <v>0.1820082199546485</v>
+        <v>0.1594460227272727</v>
       </c>
       <c r="K3">
-        <v>0.1674815759637188</v>
+        <v>0.1461776859504132</v>
       </c>
       <c r="L3">
-        <v>0.1569940476190476</v>
+        <v>0.1349108987603306</v>
       </c>
     </row>
   </sheetData>
